--- a/reports/fd0e0657-9dee-4923-bc8e-319996a08cb6/2025/07/report_______________________________07_2025.xlsx
+++ b/reports/fd0e0657-9dee-4923-bc8e-319996a08cb6/2025/07/report_______________________________07_2025.xlsx
@@ -46,10 +46,7 @@
     <t>/07</t>
   </si>
   <si>
-    <t xml:space="preserve">Уговор бр </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 221638/1-2022</t>
+    <t>Уговор бр  221638/1-2022-U од 28.05.2024</t>
   </si>
   <si>
     <t>Прималац (Добављач):</t>
@@ -64,15 +61,15 @@
     <t>Рачун примаоца:</t>
   </si>
   <si>
-    <t>340-11016097-24</t>
-  </si>
-  <si>
-    <t>Матични број 28176317</t>
+    <t>Матични број</t>
   </si>
   <si>
     <t>ПИБ 109029692</t>
   </si>
   <si>
+    <t>матични број 28176317</t>
+  </si>
+  <si>
     <t>Позив на број одобрења</t>
   </si>
   <si>
@@ -85,13 +82,16 @@
     <t>Напомена:</t>
   </si>
   <si>
-    <t>Наплаћен износ у undefined саобраћају у јулу периоду</t>
-  </si>
-  <si>
-    <t>01.07.2025 do 31.07.2025</t>
+    <t>Наплаћен износ у postpaid саобраћају у периоду</t>
+  </si>
+  <si>
+    <t>1.07.2025 do 31.07.2025</t>
   </si>
   <si>
     <t>на хуманитарном броју</t>
+  </si>
+  <si>
+    <t>1389</t>
   </si>
   <si>
     <t>Подносилац захтева:</t>
@@ -839,7 +839,7 @@
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>9</v>
@@ -855,9 +855,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="13"/>
-      <c r="C19" s="13" t="s">
-        <v>11</v>
-      </c>
+      <c r="C19" s="13"/>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
@@ -880,12 +878,12 @@
     </row>
     <row r="21" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
       <c r="D21" s="15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
@@ -920,7 +918,7 @@
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -966,13 +964,11 @@
     </row>
     <row r="27" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
-      <c r="D27" s="23" t="s">
-        <v>16</v>
-      </c>
+      <c r="D27" s="23"/>
       <c r="E27" s="24"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -985,7 +981,7 @@
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
       <c r="D28" s="25" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E28" s="26"/>
       <c r="F28" s="13"/>
@@ -999,10 +995,12 @@
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E29" s="17"/>
-      <c r="F29" s="13"/>
+      <c r="F29" s="13" t="s">
+        <v>17</v>
+      </c>
       <c r="G29" s="13"/>
       <c r="H29" s="13"/>
       <c r="I29" s="13"/>
@@ -1010,12 +1008,12 @@
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
       <c r="D30" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
@@ -1050,12 +1048,12 @@
     </row>
     <row r="33" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B33" s="10"/>
       <c r="C33" s="11"/>
       <c r="D33" s="31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E33" s="31"/>
       <c r="F33" s="31"/>
@@ -1114,12 +1112,12 @@
     </row>
     <row r="38" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
       <c r="D38" s="27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E38" s="36"/>
       <c r="F38" s="10"/>
@@ -1134,7 +1132,7 @@
       <c r="C39" s="13"/>
       <c r="D39" s="12"/>
       <c r="E39" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
@@ -1147,11 +1145,13 @@
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
       <c r="D40" s="37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E40" s="38"/>
       <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
+      <c r="G40" s="13" t="s">
+        <v>25</v>
+      </c>
       <c r="H40" s="13"/>
       <c r="I40" s="1"/>
       <c r="J40" s="30"/>

--- a/reports/fd0e0657-9dee-4923-bc8e-319996a08cb6/2025/07/report_______________________________07_2025.xlsx
+++ b/reports/fd0e0657-9dee-4923-bc8e-319996a08cb6/2025/07/report_______________________________07_2025.xlsx
@@ -82,7 +82,7 @@
     <t>Напомена:</t>
   </si>
   <si>
-    <t>Наплаћен износ у postpaid саобраћају у периоду</t>
+    <t>Наплаћен износ у prepaid саобраћају у периоду</t>
   </si>
   <si>
     <t>1.07.2025 do 31.07.2025</t>
